--- a/app/src/main/assets/Komatsu_Can.xlsx
+++ b/app/src/main/assets/Komatsu_Can.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rricotti\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E99BC954-F2CC-49A3-AFAC-C766B9845A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B743EF-16E3-4DBA-8E10-CB477AD4AD31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FBD1A101-A936-489B-942D-557FED93F0CD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FBD1A101-A936-489B-942D-557FED93F0CD}"/>
   </bookViews>
   <sheets>
     <sheet name="KOMATSU CAN" sheetId="1" r:id="rId1"/>
+    <sheet name="CAT_D6_N" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="36">
   <si>
     <t>LEICA</t>
   </si>
@@ -90,6 +91,60 @@
   </si>
   <si>
     <t>X</t>
+  </si>
+  <si>
+    <t>CAT</t>
+  </si>
+  <si>
+    <t>0x1CF00D22</t>
+  </si>
+  <si>
+    <t>00=MAN</t>
+  </si>
+  <si>
+    <t>02=AUTO</t>
+  </si>
+  <si>
+    <t>22=AUTO -OFFSET TOGGLE</t>
+  </si>
+  <si>
+    <t>12=AUTO +OFFSET TOGGLE</t>
+  </si>
+  <si>
+    <t>20=MAN -OFFSET TOGGLE</t>
+  </si>
+  <si>
+    <t>10=MAN +OFFSET TOGGLE</t>
+  </si>
+  <si>
+    <t>0X18FE3285</t>
+  </si>
+  <si>
+    <t>0X18FE3185</t>
+  </si>
+  <si>
+    <t>50mS</t>
+  </si>
+  <si>
+    <t>0X18EEFF85</t>
+  </si>
+  <si>
+    <t>1S</t>
+  </si>
+  <si>
+    <t>LEFT</t>
+  </si>
+  <si>
+    <t>RIGHT</t>
+  </si>
+  <si>
+    <t>0-255</t>
+  </si>
+  <si>
+    <t>FF</t>
+  </si>
+  <si>
+    <t>F2=UP F1=DOWN   (F2 BY DEFAULT)</t>
   </si>
 </sst>
 </file>
@@ -576,4 +631,210 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DD15F16-0CCB-4512-886D-B05153C08498}">
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.109375" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="L6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/app/src/main/assets/Komatsu_Can.xlsx
+++ b/app/src/main/assets/Komatsu_Can.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rricotti\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B743EF-16E3-4DBA-8E10-CB477AD4AD31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8A5EFA-39A0-4992-A843-5527DE7BDE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FBD1A101-A936-489B-942D-557FED93F0CD}"/>
   </bookViews>
   <sheets>
     <sheet name="KOMATSU CAN" sheetId="1" r:id="rId1"/>
-    <sheet name="CAT_D6_N" sheetId="2" r:id="rId2"/>
+    <sheet name="CAT" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="48">
   <si>
     <t>LEICA</t>
   </si>
@@ -93,9 +93,6 @@
     <t>X</t>
   </si>
   <si>
-    <t>CAT</t>
-  </si>
-  <si>
     <t>0x1CF00D22</t>
   </si>
   <si>
@@ -126,12 +123,6 @@
     <t>50mS</t>
   </si>
   <si>
-    <t>0X18EEFF85</t>
-  </si>
-  <si>
-    <t>1S</t>
-  </si>
-  <si>
     <t>LEFT</t>
   </si>
   <si>
@@ -145,6 +136,51 @@
   </si>
   <si>
     <t>F2=UP F1=DOWN   (F2 BY DEFAULT)</t>
+  </si>
+  <si>
+    <t>0X18FE3385</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>F2=RIGHT F1=LEFT   (F2 BY DEFAULT)</t>
+  </si>
+  <si>
+    <t>CAT D6N</t>
+  </si>
+  <si>
+    <t>CAT 12M</t>
+  </si>
+  <si>
+    <t>MAP D1</t>
+  </si>
+  <si>
+    <t>MAP D2</t>
+  </si>
+  <si>
+    <t>MAP D3</t>
+  </si>
+  <si>
+    <t>13=TRIGGER AUTO LEFT TOGGLE RITORNA 03</t>
+  </si>
+  <si>
+    <t>01=TRIGGER AUTO RIGHT TOGGLE RITORNA 00</t>
+  </si>
+  <si>
+    <t>20=OFFSET DOWN</t>
+  </si>
+  <si>
+    <t>10=OFFSET UP</t>
+  </si>
+  <si>
+    <t>02=OFFSET DOWN</t>
+  </si>
+  <si>
+    <t>01=OFFSET UP</t>
+  </si>
+  <si>
+    <t>10=AUTO SIDESHIFT TOGGLE</t>
   </si>
 </sst>
 </file>
@@ -635,14 +671,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DD15F16-0CCB-4512-886D-B05153C08498}">
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="37.109375" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -677,40 +713,40 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -721,67 +757,94 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" t="s">
         <v>28</v>
-      </c>
-      <c r="N4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>8</v>
       </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" t="s">
+        <v>31</v>
+      </c>
       <c r="L6" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="N6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
@@ -807,27 +870,91 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C17" t="s">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C18" t="s">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C19" t="s">
-        <v>25</v>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" t="s">
+        <v>31</v>
+      </c>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E26" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F27" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/app/src/main/assets/Komatsu_Can.xlsx
+++ b/app/src/main/assets/Komatsu_Can.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rricotti\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8A5EFA-39A0-4992-A843-5527DE7BDE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5596F1-8B0B-418D-A964-74042558D951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FBD1A101-A936-489B-942D-557FED93F0CD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{FBD1A101-A936-489B-942D-557FED93F0CD}"/>
   </bookViews>
   <sheets>
     <sheet name="KOMATSU CAN" sheetId="1" r:id="rId1"/>
     <sheet name="CAT" sheetId="2" r:id="rId2"/>
+    <sheet name="JOHN DEERE" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="65">
   <si>
     <t>LEICA</t>
   </si>
@@ -181,16 +182,74 @@
   </si>
   <si>
     <t>10=AUTO SIDESHIFT TOGGLE</t>
+  </si>
+  <si>
+    <t>00CF00D80</t>
+  </si>
+  <si>
+    <t>03=AUTO</t>
+  </si>
+  <si>
+    <t>02=MAN</t>
+  </si>
+  <si>
+    <t>12=MAN +OFF</t>
+  </si>
+  <si>
+    <t>22=MAN -OFF</t>
+  </si>
+  <si>
+    <t>13=AUTO +OFF</t>
+  </si>
+  <si>
+    <t>23=AUTO -OFF</t>
+  </si>
+  <si>
+    <t>00EFFF85</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>1A</t>
+  </si>
+  <si>
+    <t>4E</t>
+  </si>
+  <si>
+    <t>CONTROL 50MS</t>
+  </si>
+  <si>
+    <t>10000=MAX UP</t>
+  </si>
+  <si>
+    <t>LEFT VALUE 20000=0</t>
+  </si>
+  <si>
+    <t>30000=MAX DW</t>
+  </si>
+  <si>
+    <t>ATTENZIONE AI VALOREI TROPPO LONTANI DA 20.000</t>
+  </si>
+  <si>
+    <t>JD 700L</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -216,11 +275,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -964,4 +1024,197 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B40406C-6026-4A37-851E-C8F4562247BC}">
+  <dimension ref="A1:P20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="1"/>
+      <c r="L3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:H5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/app/src/main/assets/Komatsu_Can.xlsx
+++ b/app/src/main/assets/Komatsu_Can.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rricotti\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5596F1-8B0B-418D-A964-74042558D951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4486EC7-C800-4B82-9F31-31B7BBEB121E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{FBD1A101-A936-489B-942D-557FED93F0CD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FBD1A101-A936-489B-942D-557FED93F0CD}"/>
   </bookViews>
   <sheets>
     <sheet name="KOMATSU CAN" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="94">
   <si>
     <t>LEICA</t>
   </si>
@@ -88,9 +88,6 @@
     <t>D7</t>
   </si>
   <si>
-    <t>0=MAN 1=AUTO</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
@@ -100,9 +97,6 @@
     <t>00=MAN</t>
   </si>
   <si>
-    <t>02=AUTO</t>
-  </si>
-  <si>
     <t>22=AUTO -OFFSET TOGGLE</t>
   </si>
   <si>
@@ -187,9 +181,6 @@
     <t>00CF00D80</t>
   </si>
   <si>
-    <t>03=AUTO</t>
-  </si>
-  <si>
     <t>02=MAN</t>
   </si>
   <si>
@@ -233,6 +224,102 @@
   </si>
   <si>
     <t>JD 700L</t>
+  </si>
+  <si>
+    <t>CAT D6K2</t>
+  </si>
+  <si>
+    <t>03=AUTO persistent</t>
+  </si>
+  <si>
+    <t>02=AUTO toggle</t>
+  </si>
+  <si>
+    <t>0=MAN 1=AUTO persistent</t>
+  </si>
+  <si>
+    <t>JD K SERIES</t>
+  </si>
+  <si>
+    <t>se smetti di inviare cade automatico</t>
+  </si>
+  <si>
+    <t>CAT D4 Next Gen</t>
+  </si>
+  <si>
+    <t>00=AUTO persisten</t>
+  </si>
+  <si>
+    <t>20=AUTO -OFFSET TOGGLE</t>
+  </si>
+  <si>
+    <t>10=AUTO +OFFSET TOGGLE</t>
+  </si>
+  <si>
+    <t>22=MAN -OFFSET TOGGLE</t>
+  </si>
+  <si>
+    <t>12=MAN +OFFSET TOGGLE</t>
+  </si>
+  <si>
+    <t>18EEFF85</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>F0</t>
+  </si>
+  <si>
+    <t>B0</t>
+  </si>
+  <si>
+    <t>SEND 1 WHEN TO SAY MACHINE YOU ARE CONNECTED</t>
+  </si>
+  <si>
+    <t>0CF00DD5</t>
+  </si>
+  <si>
+    <t>GP GRADER</t>
+  </si>
+  <si>
+    <t>10 AUTO LEFT TOGGLE</t>
+  </si>
+  <si>
+    <t>01 AUTO RIGHT TOGGLE</t>
+  </si>
+  <si>
+    <t>F0=NULL</t>
+  </si>
+  <si>
+    <t>F1=OFFSET + TOGGLE</t>
+  </si>
+  <si>
+    <t>F2=OFFSET - TOGGLE</t>
+  </si>
+  <si>
+    <t>ID=217058773x,Type=D,Length=8,Data=FF0000F0FFFFFFFF</t>
+  </si>
+  <si>
+    <t>ROTATION SENSOR GRADER GP</t>
+  </si>
+  <si>
+    <t>0CF014D5</t>
+  </si>
+  <si>
+    <t>LSB</t>
+  </si>
+  <si>
+    <t>MSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FORMULA TILT ROTATOR OFFSET 200</t>
+  </si>
+  <si>
+    <t>ORARIO VA IN NEGATIVO</t>
+  </si>
+  <si>
+    <t>0E bladshake enabled</t>
   </si>
 </sst>
 </file>
@@ -277,10 +364,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -621,7 +708,7 @@
     <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -674,14 +761,14 @@
       <c r="B3">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1"/>
+      <c r="F3" s="2"/>
       <c r="M3" t="s">
         <v>6</v>
       </c>
@@ -699,25 +786,25 @@
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -731,7 +818,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DD15F16-0CCB-4512-886D-B05153C08498}">
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
@@ -773,248 +860,320 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2">
         <v>8</v>
       </c>
       <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
         <v>30</v>
       </c>
-      <c r="D2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" t="s">
-        <v>32</v>
-      </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" t="s">
         <v>27</v>
       </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>8</v>
       </c>
       <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
         <v>30</v>
       </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N6" t="s">
-        <v>34</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" t="s">
         <v>38</v>
       </c>
-      <c r="E24" t="s">
-        <v>39</v>
-      </c>
-      <c r="F24" t="s">
-        <v>40</v>
-      </c>
       <c r="G24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F25" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E27" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34">
+        <v>8</v>
+      </c>
+      <c r="C34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C35" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C36" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C37" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C38" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C39" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1028,12 +1187,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B40406C-6026-4A37-851E-C8F4562247BC}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.77734375" customWidth="1"/>
     <col min="8" max="8" width="21.33203125" customWidth="1"/>
     <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
@@ -1070,138 +1231,273 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B2">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E2">
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>20</v>
       </c>
       <c r="H2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="I2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="L3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E5" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="L3" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="E4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="E5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="1"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="L5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>23</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>82</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B15">
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C17" t="s">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C20" t="s">
-        <v>54</v>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" t="s">
+        <v>82</v>
+      </c>
+      <c r="F24" t="s">
+        <v>83</v>
+      </c>
+      <c r="G24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H24" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" t="s">
+        <v>29</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F26" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" t="s">
+        <v>89</v>
+      </c>
+      <c r="F31" t="s">
+        <v>90</v>
+      </c>
+      <c r="G31" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" t="s">
+        <v>29</v>
+      </c>
+      <c r="I31" t="s">
+        <v>29</v>
+      </c>
+      <c r="J31" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K32" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
